--- a/data/paired_samples.xlsx
+++ b/data/paired_samples.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4a1556a8262104be/Artigos^J Capítulos e Eventos/Índices de Intertextualidade Lexical/indices-of-intertextuality/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{7E8AB6B1-04BF-4809-BC22-FD14D4144C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCCCABE2-A75E-494C-923A-EA48E9305374}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{7E8AB6B1-04BF-4809-BC22-FD14D4144C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FDB66F4-52CF-41C8-81C7-65928842B47F}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00F106DD-3D88-4443-A4B9-C9162EBDDC03}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00F106DD-3D88-4443-A4B9-C9162EBDDC03}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -53,307 +53,307 @@
     <t>301CUL073</t>
   </si>
   <si>
+    <t>608CXL226</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-27</t>
+  </si>
+  <si>
+    <t>406CUL293</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-10</t>
+  </si>
+  <si>
+    <t>407CQL123</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-12</t>
+  </si>
+  <si>
+    <t>603CWL193</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-18</t>
+  </si>
+  <si>
+    <t>134CUL236</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-19</t>
+  </si>
+  <si>
+    <t>106CWL031</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-77</t>
+  </si>
+  <si>
+    <t>105CWL061</t>
+  </si>
+  <si>
+    <t>106CWL030</t>
+  </si>
+  <si>
+    <t>504C-L101</t>
+  </si>
+  <si>
+    <t>516CZL125</t>
+  </si>
+  <si>
+    <t>603CWL194</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-30</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-31</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-51</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-61</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-71</t>
+  </si>
+  <si>
+    <t>102CTL003</t>
+  </si>
+  <si>
+    <t>105CWL039</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-16</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-54</t>
+  </si>
+  <si>
+    <t>117CWL009</t>
+  </si>
+  <si>
+    <t>301CUL075</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-03</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-34</t>
+  </si>
+  <si>
+    <t>107CYL010</t>
+  </si>
+  <si>
+    <t>112C-L016</t>
+  </si>
+  <si>
+    <t>113CWL018</t>
+  </si>
+  <si>
+    <t>119CWL042</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-44</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-50</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-53</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-64</t>
+  </si>
+  <si>
+    <t>501C-L077</t>
+  </si>
+  <si>
+    <t>530C-L207</t>
+  </si>
+  <si>
+    <t>530C-L211</t>
+  </si>
+  <si>
+    <t>609CWL239</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-05</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-41</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-65</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-75</t>
+  </si>
+  <si>
+    <t>119CWL041</t>
+  </si>
+  <si>
+    <t>120CUL044</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-81</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-91</t>
+  </si>
+  <si>
+    <t>110CYL070</t>
+  </si>
+  <si>
+    <t>150CZL269</t>
+  </si>
+  <si>
+    <t>301CUL076</t>
+  </si>
+  <si>
+    <t>513C-L156</t>
+  </si>
+  <si>
+    <t>517CWL088</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-01</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-23</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-29</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-38</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-78</t>
+  </si>
+  <si>
+    <t>513C-L142</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-46</t>
+  </si>
+  <si>
+    <t>112C-L015</t>
+  </si>
+  <si>
+    <t>401CVL007</t>
+  </si>
+  <si>
+    <t>513C-L150</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-09</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-55</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-82</t>
+  </si>
+  <si>
+    <t>513C-L171</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-21</t>
+  </si>
+  <si>
+    <t>105CWL063</t>
+  </si>
+  <si>
+    <t>609CWL242</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-06</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-36</t>
+  </si>
+  <si>
+    <t>502C-L084</t>
+  </si>
+  <si>
+    <t>533C-L249</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-13</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-33</t>
+  </si>
+  <si>
+    <t>318C-L294</t>
+  </si>
+  <si>
+    <t>513C-L165</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-73</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-84</t>
+  </si>
+  <si>
+    <t>112C-L013</t>
+  </si>
+  <si>
+    <t>609CWL240</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-45</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-66</t>
+  </si>
+  <si>
+    <t>530C-L218</t>
+  </si>
+  <si>
+    <t>530C-L222</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-07</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-42</t>
+  </si>
+  <si>
+    <t>108CXL199</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-79</t>
+  </si>
+  <si>
+    <t>601CZL183</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-59</t>
+  </si>
+  <si>
+    <t>609CWL260</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-32</t>
+  </si>
+  <si>
+    <t>119CWL047</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-11</t>
+  </si>
+  <si>
+    <t>530C-L221</t>
+  </si>
+  <si>
+    <t>Carta-Extraordinaria-49</t>
+  </si>
+  <si>
     <t>Carta-Extraordinaria-08</t>
-  </si>
-  <si>
-    <t>608CXL226</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-27</t>
-  </si>
-  <si>
-    <t>406CUL293</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-10</t>
-  </si>
-  <si>
-    <t>407CQL123</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-12</t>
-  </si>
-  <si>
-    <t>603CWL193</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-18</t>
-  </si>
-  <si>
-    <t>134CUL236</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-19</t>
-  </si>
-  <si>
-    <t>106CWL031</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-77</t>
-  </si>
-  <si>
-    <t>105CWL061</t>
-  </si>
-  <si>
-    <t>106CWL030</t>
-  </si>
-  <si>
-    <t>504C-L101</t>
-  </si>
-  <si>
-    <t>516CZL125</t>
-  </si>
-  <si>
-    <t>603CWL194</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-30</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-31</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-51</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-61</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-71</t>
-  </si>
-  <si>
-    <t>102CTL003</t>
-  </si>
-  <si>
-    <t>105CWL039</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-16</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-54</t>
-  </si>
-  <si>
-    <t>117CWL009</t>
-  </si>
-  <si>
-    <t>301CUL075</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-03</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-34</t>
-  </si>
-  <si>
-    <t>107CYL010</t>
-  </si>
-  <si>
-    <t>112C-L016</t>
-  </si>
-  <si>
-    <t>113CWL018</t>
-  </si>
-  <si>
-    <t>119CWL042</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-44</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-50</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-53</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-64</t>
-  </si>
-  <si>
-    <t>501C-L077</t>
-  </si>
-  <si>
-    <t>530C-L207</t>
-  </si>
-  <si>
-    <t>530C-L211</t>
-  </si>
-  <si>
-    <t>609CWL239</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-05</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-41</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-65</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-75</t>
-  </si>
-  <si>
-    <t>119CWL041</t>
-  </si>
-  <si>
-    <t>120CUL044</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-81</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-91</t>
-  </si>
-  <si>
-    <t>110CYL070</t>
-  </si>
-  <si>
-    <t>150CZL269</t>
-  </si>
-  <si>
-    <t>301CUL076</t>
-  </si>
-  <si>
-    <t>513C-L156</t>
-  </si>
-  <si>
-    <t>517CWL088</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-01</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-23</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-29</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-38</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-78</t>
-  </si>
-  <si>
-    <t>513C-L142</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-46</t>
-  </si>
-  <si>
-    <t>112C-L015</t>
-  </si>
-  <si>
-    <t>401CVL007</t>
-  </si>
-  <si>
-    <t>513C-L150</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-09</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-55</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-82</t>
-  </si>
-  <si>
-    <t>513C-L171</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-21</t>
-  </si>
-  <si>
-    <t>105CWL063</t>
-  </si>
-  <si>
-    <t>609CWL242</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-06</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-36</t>
-  </si>
-  <si>
-    <t>502C-L084</t>
-  </si>
-  <si>
-    <t>533C-L249</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-13</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-33</t>
-  </si>
-  <si>
-    <t>318C-L294</t>
-  </si>
-  <si>
-    <t>513C-L165</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-73</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-84</t>
-  </si>
-  <si>
-    <t>112C-L013</t>
-  </si>
-  <si>
-    <t>609CWL240</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-45</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-66</t>
-  </si>
-  <si>
-    <t>530C-L218</t>
-  </si>
-  <si>
-    <t>530C-L222</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-07</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-42</t>
-  </si>
-  <si>
-    <t>108CXL199</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-79</t>
-  </si>
-  <si>
-    <t>601CZL183</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-59</t>
-  </si>
-  <si>
-    <t>609CWL260</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-32</t>
-  </si>
-  <si>
-    <t>119CWL047</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-11</t>
-  </si>
-  <si>
-    <t>530C-L221</t>
-  </si>
-  <si>
-    <t>Carta-Extraordinaria-49</t>
   </si>
 </sst>
 </file>
@@ -406,6 +406,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -752,7 +756,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -760,10 +764,10 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -771,10 +775,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -782,10 +786,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -793,10 +797,10 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -804,10 +808,10 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -815,10 +819,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -826,10 +830,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -837,10 +841,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -848,10 +852,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -859,10 +863,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -870,10 +874,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -881,10 +885,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -892,10 +896,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -903,10 +907,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -914,10 +918,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -925,10 +929,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -936,10 +940,10 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -947,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -958,10 +962,10 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -969,10 +973,10 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -980,10 +984,10 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -991,10 +995,10 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1002,10 +1006,10 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1013,10 +1017,10 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1024,10 +1028,10 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1035,10 +1039,10 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1046,10 +1050,10 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1057,10 +1061,10 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1068,10 +1072,10 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1079,10 +1083,10 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1090,10 +1094,10 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" t="s">
         <v>65</v>
-      </c>
-      <c r="C33" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1101,10 +1105,10 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1112,10 +1116,10 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1123,10 +1127,10 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1134,10 +1138,10 @@
         <v>22</v>
       </c>
       <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" t="s">
         <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1145,10 +1149,10 @@
         <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1156,10 +1160,10 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1167,10 +1171,10 @@
         <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1178,10 +1182,10 @@
         <v>24</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1189,10 +1193,10 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1200,10 +1204,10 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1211,10 +1215,10 @@
         <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1222,10 +1226,10 @@
         <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1233,10 +1237,10 @@
         <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1244,10 +1248,10 @@
         <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1255,10 +1259,10 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" t="s">
         <v>95</v>
-      </c>
-      <c r="C48" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1266,10 +1270,10 @@
         <v>38</v>
       </c>
       <c r="B49" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" t="s">
         <v>97</v>
-      </c>
-      <c r="C49" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1277,10 +1281,10 @@
         <v>39</v>
       </c>
       <c r="B50" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" t="s">
         <v>99</v>
-      </c>
-      <c r="C50" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1288,10 +1292,10 @@
         <v>42</v>
       </c>
       <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" t="s">
         <v>101</v>
-      </c>
-      <c r="C51" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1299,10 +1303,10 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" t="s">
         <v>103</v>
-      </c>
-      <c r="C52" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
